--- a/tests/golden-cases/G-M01/expected/output.xlsx.xlsx
+++ b/tests/golden-cases/G-M01/expected/output.xlsx.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,10 +598,15 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
+          <t>statement_occurrence</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>statement_opening_balance</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>statement_closing_balance</t>
         </is>
@@ -676,10 +681,15 @@
       <c r="AI2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
         <v>1000</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>1150</v>
       </c>
     </row>
@@ -747,10 +757,15 @@
       <c r="AI3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
         <v>1000</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>1150</v>
       </c>
     </row>
@@ -765,7 +780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,85 +791,90 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>statement_occurrence</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>account_iban</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>account_other_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>statement_number</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sequence_number</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>opening_balance_date</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>opening_balance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>closing_balance_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>closing_balance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>closing_available_balance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>total_credits</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>total_debits</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>credit_count</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>debit_count</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>transaction_count</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>source_format</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>information_loss_flags</t>
         </is>
@@ -868,48 +888,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>DE75512108001245126199</t>
         </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>46024</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1000</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>46025</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>1150</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>200</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>50</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>mt940</t>
         </is>
